--- a/法宝属性.xlsx
+++ b/法宝属性.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="196">
   <si>
     <t>法宝名</t>
   </si>
@@ -217,7 +217,7 @@
     <t>金锋无影</t>
   </si>
   <si>
-    <t>[1 0]
+    <t>[0 1]
 [1 1]
 [1 1]</t>
   </si>
@@ -308,11 +308,6 @@
   </si>
   <si>
     <t>青阳唤春</t>
-  </si>
-  <si>
-    <t>[0 1]
-[1 1]
-[1 1]</t>
   </si>
   <si>
     <t>太昊司春</t>
@@ -1286,9 +1281,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2701,7 +2695,7 @@
       <c r="I33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K33" t="s">
@@ -3114,13 +3108,13 @@
       <c r="G46">
         <v>15</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46" s="2" t="s">
+      <c r="H46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="J46" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K46" t="s">
@@ -3149,13 +3143,13 @@
       <c r="G47">
         <v>15</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I47" s="2" t="s">
+      <c r="H47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="J47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K47" t="s">
@@ -3165,7 +3159,7 @@
     <row r="48" spans="1:11">
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-      <c r="J48" s="2"/>
+      <c r="J48" s="1"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K47" etc:filterBottomFollowUsedRange="0">
@@ -3174,7 +3168,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="K46 A46:G46 A1:K31 A32:G32 I32:K32 A34:K45" numberStoredAsText="1"/>
+    <ignoredError sqref="A34:K44 A45 C45:K45 I32:K32 A32:G32 A1:K31 A46:G46 K46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4603,7 +4597,7 @@
         <v>78</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>64</v>
@@ -4635,10 +4629,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C47">
         <v>64</v>
@@ -4723,7 +4717,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -4845,7 +4839,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -4875,7 +4869,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -4904,7 +4898,7 @@
         <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4933,7 +4927,7 @@
         <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -4962,12 +4956,12 @@
         <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -5089,7 +5083,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -5119,7 +5113,7 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -5148,7 +5142,7 @@
         <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -5177,7 +5171,7 @@
         <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -5206,12 +5200,12 @@
         <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -5241,7 +5235,7 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -5270,7 +5264,7 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -5299,7 +5293,7 @@
         <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -5328,12 +5322,12 @@
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
@@ -5363,12 +5357,12 @@
         <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -5490,7 +5484,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
@@ -5525,7 +5519,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -5549,13 +5543,13 @@
         <v>29</v>
       </c>
       <c r="I28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -5578,13 +5572,13 @@
         <v>29</v>
       </c>
       <c r="I29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -5607,13 +5601,13 @@
         <v>29</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -5636,18 +5630,18 @@
         <v>29</v>
       </c>
       <c r="I31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -5677,12 +5671,12 @@
         <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s">
         <v>68</v>
@@ -5712,12 +5706,12 @@
         <v>30</v>
       </c>
       <c r="K33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
@@ -5839,7 +5833,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
@@ -5874,7 +5868,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -5904,7 +5898,7 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5933,7 +5927,7 @@
         <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5962,7 +5956,7 @@
         <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5991,12 +5985,12 @@
         <v>19</v>
       </c>
       <c r="K42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -6026,12 +6020,12 @@
         <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
@@ -6066,7 +6060,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -6096,15 +6090,15 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>64</v>
@@ -6125,21 +6119,21 @@
         <v>29</v>
       </c>
       <c r="I46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J46" t="s">
         <v>30</v>
       </c>
       <c r="K46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C47">
         <v>64</v>
@@ -6160,13 +6154,13 @@
         <v>29</v>
       </c>
       <c r="I47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J47" t="s">
         <v>30</v>
       </c>
       <c r="K47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -6224,7 +6218,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6346,7 +6340,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -6468,7 +6462,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -6590,7 +6584,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -6712,7 +6706,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -6747,7 +6741,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -6869,7 +6863,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -6991,7 +6985,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
@@ -7026,7 +7020,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -7148,7 +7142,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -7183,7 +7177,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
         <v>68</v>
@@ -7218,7 +7212,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
@@ -7242,7 +7236,7 @@
         <v>29</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
@@ -7271,7 +7265,7 @@
         <v>29</v>
       </c>
       <c r="I35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J35" t="s">
         <v>17</v>
@@ -7300,7 +7294,7 @@
         <v>29</v>
       </c>
       <c r="I36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J36" t="s">
         <v>18</v>
@@ -7329,7 +7323,7 @@
         <v>29</v>
       </c>
       <c r="I37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -7340,7 +7334,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
@@ -7375,7 +7369,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -7497,7 +7491,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -7532,7 +7526,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
@@ -7556,7 +7550,7 @@
         <v>29</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J44" t="s">
         <v>30</v>
@@ -7567,7 +7561,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
@@ -7602,10 +7596,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>64</v>
@@ -7637,7 +7631,7 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
         <v>55</v>
@@ -7725,7 +7719,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7847,7 +7841,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -7877,7 +7871,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -7906,7 +7900,7 @@
         <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -7935,7 +7929,7 @@
         <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -7964,12 +7958,12 @@
         <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -7999,7 +7993,7 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -8028,7 +8022,7 @@
         <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -8057,7 +8051,7 @@
         <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -8086,12 +8080,12 @@
         <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -8121,7 +8115,7 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -8150,7 +8144,7 @@
         <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8179,7 +8173,7 @@
         <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -8208,12 +8202,12 @@
         <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -8243,12 +8237,12 @@
         <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -8278,7 +8272,7 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -8307,7 +8301,7 @@
         <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -8336,7 +8330,7 @@
         <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -8365,12 +8359,12 @@
         <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
@@ -8400,7 +8394,7 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -8429,7 +8423,7 @@
         <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -8458,7 +8452,7 @@
         <v>18</v>
       </c>
       <c r="K25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -8487,12 +8481,12 @@
         <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -8522,12 +8516,12 @@
         <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -8557,7 +8551,7 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -8586,7 +8580,7 @@
         <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -8615,7 +8609,7 @@
         <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -8644,12 +8638,12 @@
         <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -8679,12 +8673,12 @@
         <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -8714,7 +8708,7 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -8743,7 +8737,7 @@
         <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -8772,7 +8766,7 @@
         <v>18</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -8801,12 +8795,12 @@
         <v>19</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -8836,12 +8830,12 @@
         <v>30</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -8871,7 +8865,7 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -8900,7 +8894,7 @@
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -8929,7 +8923,7 @@
         <v>18</v>
       </c>
       <c r="K40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -8958,12 +8952,12 @@
         <v>19</v>
       </c>
       <c r="K41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -8993,12 +8987,12 @@
         <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -9028,15 +9022,15 @@
         <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>64</v>
@@ -9063,15 +9057,15 @@
         <v>30</v>
       </c>
       <c r="K44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" t="s">
         <v>140</v>
-      </c>
-      <c r="B45" t="s">
-        <v>141</v>
       </c>
       <c r="C45">
         <v>64</v>
@@ -9098,7 +9092,7 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -9156,7 +9150,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -9278,7 +9272,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -9400,7 +9394,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -9430,7 +9424,7 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -9459,7 +9453,7 @@
         <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -9488,7 +9482,7 @@
         <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -9517,12 +9511,12 @@
         <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -9552,7 +9546,7 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -9581,7 +9575,7 @@
         <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -9610,7 +9604,7 @@
         <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -9639,12 +9633,12 @@
         <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -9766,7 +9760,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
@@ -9801,10 +9795,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" t="s">
         <v>148</v>
-      </c>
-      <c r="B23" t="s">
-        <v>149</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -9923,10 +9917,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27">
         <v>32</v>
@@ -9958,7 +9952,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -9982,7 +9976,7 @@
         <v>29</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -10011,7 +10005,7 @@
         <v>29</v>
       </c>
       <c r="I29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
@@ -10040,7 +10034,7 @@
         <v>29</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -10069,7 +10063,7 @@
         <v>29</v>
       </c>
       <c r="I31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -10080,7 +10074,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -10115,7 +10109,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -10237,7 +10231,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -10272,7 +10266,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -10302,7 +10296,7 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -10331,7 +10325,7 @@
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -10360,7 +10354,7 @@
         <v>18</v>
       </c>
       <c r="K40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -10389,12 +10383,12 @@
         <v>19</v>
       </c>
       <c r="K41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -10424,12 +10418,12 @@
         <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -10464,10 +10458,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>64</v>
@@ -10499,7 +10493,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -10529,7 +10523,7 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -10587,7 +10581,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -10709,7 +10703,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -10831,7 +10825,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -10861,7 +10855,7 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -10890,7 +10884,7 @@
         <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -10919,7 +10913,7 @@
         <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -10948,12 +10942,12 @@
         <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -10983,7 +10977,7 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -11012,7 +11006,7 @@
         <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -11041,7 +11035,7 @@
         <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -11070,12 +11064,12 @@
         <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -11105,12 +11099,12 @@
         <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -11232,10 +11226,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -11262,7 +11256,7 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -11291,7 +11285,7 @@
         <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -11320,7 +11314,7 @@
         <v>18</v>
       </c>
       <c r="K25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -11349,15 +11343,15 @@
         <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27">
         <v>32</v>
@@ -11384,12 +11378,12 @@
         <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -11413,13 +11407,13 @@
         <v>29</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -11442,13 +11436,13 @@
         <v>29</v>
       </c>
       <c r="I29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -11471,13 +11465,13 @@
         <v>29</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -11500,18 +11494,18 @@
         <v>29</v>
       </c>
       <c r="I31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -11541,12 +11535,12 @@
         <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -11668,7 +11662,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -11703,7 +11697,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -11733,7 +11727,7 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -11762,7 +11756,7 @@
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -11791,7 +11785,7 @@
         <v>18</v>
       </c>
       <c r="K40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -11820,12 +11814,12 @@
         <v>19</v>
       </c>
       <c r="K41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -11855,12 +11849,12 @@
         <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -11895,10 +11889,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>64</v>
@@ -11925,12 +11919,12 @@
         <v>30</v>
       </c>
       <c r="K44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -11960,7 +11954,7 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -12018,7 +12012,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -12048,15 +12042,15 @@
         <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -12083,15 +12077,15 @@
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -12118,15 +12112,15 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -12153,12 +12147,12 @@
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -12176,7 +12170,7 @@
         <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -12193,10 +12187,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -12211,7 +12205,7 @@
         <v>470</v>
       </c>
       <c r="G7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -12228,10 +12222,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -12246,7 +12240,7 @@
         <v>970</v>
       </c>
       <c r="G8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -12263,10 +12257,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -12281,7 +12275,7 @@
         <v>1920</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -12298,7 +12292,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -12316,7 +12310,7 @@
         <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -12333,10 +12327,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -12351,7 +12345,7 @@
         <v>455</v>
       </c>
       <c r="G11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -12368,10 +12362,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -12386,7 +12380,7 @@
         <v>1105</v>
       </c>
       <c r="G12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -12403,10 +12397,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C13">
         <v>32</v>
@@ -12421,7 +12415,7 @@
         <v>2255</v>
       </c>
       <c r="G13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -12438,7 +12432,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
@@ -12473,10 +12467,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -12508,10 +12502,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -12543,10 +12537,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17">
         <v>40</v>
@@ -12578,7 +12572,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -12596,7 +12590,7 @@
         <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -12608,15 +12602,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -12631,7 +12625,7 @@
         <v>305</v>
       </c>
       <c r="G19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -12643,15 +12637,15 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -12666,7 +12660,7 @@
         <v>855</v>
       </c>
       <c r="G20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -12678,15 +12672,15 @@
         <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C21">
         <v>32</v>
@@ -12701,7 +12695,7 @@
         <v>1905</v>
       </c>
       <c r="G21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -12713,12 +12707,12 @@
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
@@ -12748,15 +12742,15 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -12783,15 +12777,15 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -12818,15 +12812,15 @@
         <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C25">
         <v>40</v>
@@ -12853,12 +12847,12 @@
         <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
@@ -12876,7 +12870,7 @@
         <v>238</v>
       </c>
       <c r="G26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -12888,15 +12882,15 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -12911,7 +12905,7 @@
         <v>555</v>
       </c>
       <c r="G27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -12923,15 +12917,15 @@
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -12946,7 +12940,7 @@
         <v>1255</v>
       </c>
       <c r="G28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -12958,15 +12952,15 @@
         <v>18</v>
       </c>
       <c r="K28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C29">
         <v>32</v>
@@ -12981,7 +12975,7 @@
         <v>2505</v>
       </c>
       <c r="G29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -12993,12 +12987,12 @@
         <v>19</v>
       </c>
       <c r="K29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -13028,15 +13022,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -13063,15 +13057,15 @@
         <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -13098,15 +13092,15 @@
         <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C33">
         <v>40</v>
@@ -13133,12 +13127,12 @@
         <v>19</v>
       </c>
       <c r="K33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -13156,7 +13150,7 @@
         <v>125</v>
       </c>
       <c r="G34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -13168,15 +13162,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -13191,7 +13185,7 @@
         <v>370</v>
       </c>
       <c r="G35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -13203,15 +13197,15 @@
         <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -13226,7 +13220,7 @@
         <v>820</v>
       </c>
       <c r="G36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -13238,15 +13232,15 @@
         <v>18</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -13261,7 +13255,7 @@
         <v>1670</v>
       </c>
       <c r="G37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -13273,12 +13267,12 @@
         <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
@@ -13296,7 +13290,7 @@
         <v>4700</v>
       </c>
       <c r="G38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -13313,7 +13307,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
@@ -13348,7 +13342,7 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -13366,7 +13360,7 @@
         <v>4250</v>
       </c>
       <c r="G40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -13378,15 +13372,15 @@
         <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C41">
         <v>64</v>
@@ -13413,12 +13407,12 @@
         <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -13436,7 +13430,7 @@
         <v>5100</v>
       </c>
       <c r="G42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -13448,12 +13442,12 @@
         <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -13483,12 +13477,12 @@
         <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B44" t="s">
         <v>32</v>
@@ -13523,7 +13517,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
@@ -13553,7 +13547,7 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/法宝属性.xlsx
+++ b/法宝属性.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20010" windowHeight="16755"/>
+    <workbookView windowWidth="20010" windowHeight="16755" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="金" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="197">
   <si>
     <t>法宝名</t>
   </si>
@@ -601,6 +601,9 @@
   </si>
   <si>
     <t>真武神镯</t>
+  </si>
+  <si>
+    <t>无相无我</t>
   </si>
   <si>
     <t>邪源珠</t>
@@ -1281,8 +1284,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2654,7 +2658,7 @@
       <c r="G32">
         <v>0</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="s">
@@ -2689,13 +2693,13 @@
       <c r="G33">
         <v>0</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="1" t="s">
+      <c r="H33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K33" t="s">
@@ -3108,13 +3112,13 @@
       <c r="G46">
         <v>15</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46" s="1" t="s">
+      <c r="H46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K46" t="s">
@@ -3143,13 +3147,13 @@
       <c r="G47">
         <v>15</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I47" s="1" t="s">
+      <c r="H47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K47" t="s">
@@ -3157,9 +3161,9 @@
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K47" etc:filterBottomFollowUsedRange="0">
@@ -3168,7 +3172,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A34:K44 A45 C45:K45 I32:K32 A32:G32 A1:K31 A46:G46 K46" numberStoredAsText="1"/>
+    <ignoredError sqref="K46 A46:G46 A1:K31 A32:G32 I32:K32 C45:K45 A45 A34:K44" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10541,7 +10545,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -11944,7 +11948,7 @@
       <c r="G45">
         <v>60</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I45" t="s">
@@ -11954,6 +11958,41 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46">
+        <v>64</v>
+      </c>
+      <c r="D46">
+        <v>118</v>
+      </c>
+      <c r="E46">
+        <v>19</v>
+      </c>
+      <c r="F46">
+        <v>6400</v>
+      </c>
+      <c r="G46">
+        <v>60</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" t="s">
         <v>86</v>
       </c>
     </row>
@@ -11964,7 +12003,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K45" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K44 A45:G45 I45:K45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12012,7 +12051,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -12042,15 +12081,15 @@
         <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -12077,15 +12116,15 @@
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -12112,15 +12151,15 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -12147,12 +12186,12 @@
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -12170,7 +12209,7 @@
         <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -12187,10 +12226,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -12205,7 +12244,7 @@
         <v>470</v>
       </c>
       <c r="G7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -12222,10 +12261,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -12240,7 +12279,7 @@
         <v>970</v>
       </c>
       <c r="G8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -12257,10 +12296,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -12275,7 +12314,7 @@
         <v>1920</v>
       </c>
       <c r="G9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -12292,7 +12331,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -12310,7 +12349,7 @@
         <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -12327,10 +12366,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -12345,7 +12384,7 @@
         <v>455</v>
       </c>
       <c r="G11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -12362,10 +12401,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -12380,7 +12419,7 @@
         <v>1105</v>
       </c>
       <c r="G12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -12397,10 +12436,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C13">
         <v>32</v>
@@ -12415,7 +12454,7 @@
         <v>2255</v>
       </c>
       <c r="G13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -12432,7 +12471,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
@@ -12467,10 +12506,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -12502,10 +12541,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -12537,10 +12576,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17">
         <v>40</v>
@@ -12572,7 +12611,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -12590,7 +12629,7 @@
         <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -12602,15 +12641,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -12625,7 +12664,7 @@
         <v>305</v>
       </c>
       <c r="G19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -12637,15 +12676,15 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -12660,7 +12699,7 @@
         <v>855</v>
       </c>
       <c r="G20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -12672,15 +12711,15 @@
         <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C21">
         <v>32</v>
@@ -12695,7 +12734,7 @@
         <v>1905</v>
       </c>
       <c r="G21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -12707,12 +12746,12 @@
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
@@ -12742,15 +12781,15 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -12777,15 +12816,15 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -12812,15 +12851,15 @@
         <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C25">
         <v>40</v>
@@ -12847,12 +12886,12 @@
         <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
@@ -12870,7 +12909,7 @@
         <v>238</v>
       </c>
       <c r="G26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -12887,10 +12926,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -12905,7 +12944,7 @@
         <v>555</v>
       </c>
       <c r="G27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -12922,10 +12961,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -12940,7 +12979,7 @@
         <v>1255</v>
       </c>
       <c r="G28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -12957,10 +12996,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C29">
         <v>32</v>
@@ -12975,7 +13014,7 @@
         <v>2505</v>
       </c>
       <c r="G29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -12992,7 +13031,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -13027,10 +13066,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -13062,10 +13101,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -13097,10 +13136,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33">
         <v>40</v>
@@ -13132,7 +13171,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -13150,7 +13189,7 @@
         <v>125</v>
       </c>
       <c r="G34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -13167,10 +13206,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -13185,7 +13224,7 @@
         <v>370</v>
       </c>
       <c r="G35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -13202,10 +13241,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -13220,7 +13259,7 @@
         <v>820</v>
       </c>
       <c r="G36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -13237,10 +13276,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -13255,7 +13294,7 @@
         <v>1670</v>
       </c>
       <c r="G37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -13272,7 +13311,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
@@ -13290,7 +13329,7 @@
         <v>4700</v>
       </c>
       <c r="G38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -13307,7 +13346,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
@@ -13342,7 +13381,7 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -13360,7 +13399,7 @@
         <v>4250</v>
       </c>
       <c r="G40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -13372,12 +13411,12 @@
         <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
@@ -13407,12 +13446,12 @@
         <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -13430,7 +13469,7 @@
         <v>5100</v>
       </c>
       <c r="G42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -13447,7 +13486,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -13482,7 +13521,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B44" t="s">
         <v>32</v>
@@ -13517,7 +13556,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
@@ -13547,7 +13586,7 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/法宝属性.xlsx
+++ b/法宝属性.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20010" windowHeight="16755" activeTab="6"/>
+    <workbookView windowWidth="20010" windowHeight="16755" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="金" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">木!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">水!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">火!$A$1:$K$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">土!$A$1:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">土!$A$1:$K$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">雷!$A$1:$K$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">体!$A$1:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">体!$A$1:$K$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="200">
   <si>
     <t>法宝名</t>
   </si>
@@ -478,6 +478,9 @@
     <t>逐日镇岳</t>
   </si>
   <si>
+    <t>九州定海</t>
+  </si>
+  <si>
     <t>撼地震破锤</t>
   </si>
   <si>
@@ -488,6 +491,9 @@
   </si>
   <si>
     <t>泰山压顶</t>
+  </si>
+  <si>
+    <t>[0 1][1 1][1 1]</t>
   </si>
   <si>
     <t>十方大山</t>
@@ -496,6 +502,9 @@
     <t>[0 1 1]
 [0 1 0]
 [1 1 0]</t>
+  </si>
+  <si>
+    <t>庚辰龙脉</t>
   </si>
   <si>
     <t>雷灵珠</t>
@@ -1284,9 +1293,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2658,7 +2670,7 @@
       <c r="G32">
         <v>0</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="s">
@@ -2693,13 +2705,13 @@
       <c r="G33">
         <v>0</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="2" t="s">
+      <c r="H33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K33" t="s">
@@ -3112,13 +3124,13 @@
       <c r="G46">
         <v>15</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46" s="2" t="s">
+      <c r="H46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="J46" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K46" t="s">
@@ -3147,13 +3159,13 @@
       <c r="G47">
         <v>15</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I47" s="2" t="s">
+      <c r="H47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="J47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K47" t="s">
@@ -3161,9 +3173,9 @@
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K47" etc:filterBottomFollowUsedRange="0">
@@ -3172,7 +3184,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="K46 A46:G46 A1:K31 A32:G32 I32:K32 C45:K45 A45 A34:K44" numberStoredAsText="1"/>
+    <ignoredError sqref="A34:K44 A45 C45:K45 I32:K32 A32:G32 A1:K31 A46:G46 K46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7683,8 +7695,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="23.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -8813,13 +8828,13 @@
         <v>56</v>
       </c>
       <c r="D37">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="F37">
-        <v>8600</v>
+        <v>6400</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -8834,7 +8849,7 @@
         <v>30</v>
       </c>
       <c r="K37" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -8842,48 +8857,54 @@
         <v>135</v>
       </c>
       <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38">
+        <v>56</v>
+      </c>
+      <c r="D38">
+        <v>27</v>
+      </c>
+      <c r="E38">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <v>8600</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" t="s">
         <v>46</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>5</v>
       </c>
-      <c r="D38">
+      <c r="D39">
         <v>10</v>
       </c>
-      <c r="E38">
+      <c r="E39">
         <v>10</v>
       </c>
-      <c r="F38">
+      <c r="F39">
         <v>650</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
-      </c>
-      <c r="H38" t="s">
-        <v>29</v>
-      </c>
-      <c r="I38" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="K38" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="C39">
-        <v>12</v>
-      </c>
-      <c r="D39">
-        <v>16</v>
-      </c>
-      <c r="E39">
-        <v>16</v>
-      </c>
-      <c r="F39">
-        <v>1340</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -8895,7 +8916,7 @@
         <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K39" t="s">
         <v>82</v>
@@ -8903,16 +8924,16 @@
     </row>
     <row r="40" spans="1:11">
       <c r="C40">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D40">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E40">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F40">
-        <v>2540</v>
+        <v>1340</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -8924,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K40" t="s">
         <v>82</v>
@@ -8932,19 +8953,19 @@
     </row>
     <row r="41" spans="1:11">
       <c r="C41">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D41">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E41">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F41">
-        <v>4740</v>
+        <v>2540</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H41" t="s">
         <v>29</v>
@@ -8953,42 +8974,36 @@
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" t="s">
-        <v>136</v>
-      </c>
-      <c r="B42" t="s">
-        <v>46</v>
-      </c>
       <c r="C42">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D42">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E42">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F42">
-        <v>7100</v>
+        <v>4740</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J42" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s">
         <v>82</v>
@@ -8999,34 +9014,34 @@
         <v>137</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C43">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D43">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F43">
-        <v>10400</v>
+        <v>7100</v>
       </c>
       <c r="G43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I43" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="J43" t="s">
         <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -9034,7 +9049,7 @@
         <v>138</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <v>64</v>
@@ -9043,10 +9058,10 @@
         <v>46</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F44">
-        <v>9800</v>
+        <v>10400</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -9055,33 +9070,33 @@
         <v>29</v>
       </c>
       <c r="I44" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="J44" t="s">
         <v>30</v>
       </c>
       <c r="K44" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>139</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C45">
         <v>64</v>
       </c>
       <c r="D45">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E45">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>7850</v>
+        <v>9800</v>
       </c>
       <c r="G45">
         <v>10</v>
@@ -9096,17 +9111,87 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46">
+        <v>64</v>
+      </c>
+      <c r="D46">
+        <v>54</v>
+      </c>
+      <c r="E46">
+        <v>54</v>
+      </c>
+      <c r="F46">
+        <v>7850</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" t="s">
         <v>82</v>
       </c>
     </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47">
+        <v>64</v>
+      </c>
+      <c r="D47">
+        <v>64</v>
+      </c>
+      <c r="E47">
+        <v>64</v>
+      </c>
+      <c r="F47">
+        <v>6850</v>
+      </c>
+      <c r="G47">
+        <v>100</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K47" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K45" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K46" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L45" numberStoredAsText="1"/>
+    <ignoredError sqref="A39:L44 A1:L36 A37:C37 G37:J37 L37 A45 C45:L45 A46:G46 I46 K46:L46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9154,7 +9239,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -9276,7 +9361,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -9398,7 +9483,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -9520,7 +9605,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -9642,7 +9727,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -9764,7 +9849,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
@@ -9799,10 +9884,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -9921,10 +10006,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C27">
         <v>32</v>
@@ -9956,7 +10041,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -10078,7 +10163,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -10113,7 +10198,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -10235,7 +10320,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -10270,7 +10355,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -10392,7 +10477,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -10427,7 +10512,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -10462,7 +10547,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
@@ -10497,7 +10582,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -10585,7 +10670,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -10707,7 +10792,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -10829,7 +10914,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -10951,7 +11036,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -11073,7 +11158,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -11108,7 +11193,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -11230,10 +11315,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -11352,10 +11437,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C27">
         <v>32</v>
@@ -11387,7 +11472,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -11509,7 +11594,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -11544,7 +11629,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -11666,7 +11751,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -11701,7 +11786,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -11823,7 +11908,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -11858,7 +11943,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -11893,7 +11978,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
@@ -11928,7 +12013,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -11963,7 +12048,7 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B46" t="s">
         <v>51</v>
@@ -11997,13 +12082,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K45" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K46" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K44 A45:G45 I45:K45" numberStoredAsText="1"/>
+    <ignoredError sqref="I45:K45 A45:G45 A1:K44" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12051,7 +12136,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -12081,15 +12166,15 @@
         <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -12116,15 +12201,15 @@
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -12151,15 +12236,15 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -12186,12 +12271,12 @@
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -12209,7 +12294,7 @@
         <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -12226,10 +12311,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -12244,7 +12329,7 @@
         <v>470</v>
       </c>
       <c r="G7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -12261,10 +12346,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -12279,7 +12364,7 @@
         <v>970</v>
       </c>
       <c r="G8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -12296,10 +12381,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -12314,7 +12399,7 @@
         <v>1920</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -12331,7 +12416,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -12349,7 +12434,7 @@
         <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -12366,10 +12451,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -12384,7 +12469,7 @@
         <v>455</v>
       </c>
       <c r="G11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -12401,10 +12486,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -12419,7 +12504,7 @@
         <v>1105</v>
       </c>
       <c r="G12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -12436,10 +12521,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C13">
         <v>32</v>
@@ -12454,7 +12539,7 @@
         <v>2255</v>
       </c>
       <c r="G13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -12471,7 +12556,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
@@ -12506,10 +12591,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -12541,10 +12626,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -12576,10 +12661,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17">
         <v>40</v>
@@ -12611,7 +12696,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -12629,7 +12714,7 @@
         <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -12641,15 +12726,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -12664,7 +12749,7 @@
         <v>305</v>
       </c>
       <c r="G19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -12676,15 +12761,15 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -12699,7 +12784,7 @@
         <v>855</v>
       </c>
       <c r="G20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -12711,15 +12796,15 @@
         <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C21">
         <v>32</v>
@@ -12734,7 +12819,7 @@
         <v>1905</v>
       </c>
       <c r="G21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -12746,12 +12831,12 @@
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
@@ -12781,15 +12866,15 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -12816,15 +12901,15 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -12851,15 +12936,15 @@
         <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B25" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C25">
         <v>40</v>
@@ -12886,12 +12971,12 @@
         <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
@@ -12909,7 +12994,7 @@
         <v>238</v>
       </c>
       <c r="G26" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -12926,10 +13011,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -12944,7 +13029,7 @@
         <v>555</v>
       </c>
       <c r="G27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -12961,10 +13046,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -12979,7 +13064,7 @@
         <v>1255</v>
       </c>
       <c r="G28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -12996,10 +13081,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C29">
         <v>32</v>
@@ -13014,7 +13099,7 @@
         <v>2505</v>
       </c>
       <c r="G29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -13031,7 +13116,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -13066,10 +13151,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -13101,10 +13186,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -13136,10 +13221,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C33">
         <v>40</v>
@@ -13171,7 +13256,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -13189,7 +13274,7 @@
         <v>125</v>
       </c>
       <c r="G34" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -13206,10 +13291,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -13224,7 +13309,7 @@
         <v>370</v>
       </c>
       <c r="G35" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -13241,10 +13326,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -13259,7 +13344,7 @@
         <v>820</v>
       </c>
       <c r="G36" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -13276,10 +13361,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -13294,7 +13379,7 @@
         <v>1670</v>
       </c>
       <c r="G37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -13311,7 +13396,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
@@ -13329,7 +13414,7 @@
         <v>4700</v>
       </c>
       <c r="G38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -13346,7 +13431,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
@@ -13381,7 +13466,7 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -13399,7 +13484,7 @@
         <v>4250</v>
       </c>
       <c r="G40" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -13411,12 +13496,12 @@
         <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
@@ -13446,12 +13531,12 @@
         <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -13469,7 +13554,7 @@
         <v>5100</v>
       </c>
       <c r="G42" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -13486,7 +13571,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -13521,7 +13606,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s">
         <v>32</v>
@@ -13556,7 +13641,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
@@ -13586,7 +13671,7 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/法宝属性.xlsx
+++ b/法宝属性.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">木!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">水!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">火!$A$1:$K$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">土!$A$1:$K$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">土!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">雷!$A$1:$K$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">体!$A$1:$K$46</definedName>
   </definedNames>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="199">
   <si>
     <t>法宝名</t>
   </si>
@@ -491,9 +491,6 @@
   </si>
   <si>
     <t>泰山压顶</t>
-  </si>
-  <si>
-    <t>[0 1][1 1][1 1]</t>
   </si>
   <si>
     <t>十方大山</t>
@@ -1296,10 +1293,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3184,7 +3179,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A34:K44 A45 C45:K45 I32:K32 A32:G32 A1:K31 A46:G46 K46" numberStoredAsText="1"/>
+    <ignoredError sqref="K46 A46:G46 A1:K31 A32:G32 I32:K32 C45:K45 A45 A34:K44" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7698,14 +7693,14 @@
   <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -7740,7 +7735,7 @@
       <c r="A2" t="s">
         <v>122</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2">
@@ -7862,7 +7857,7 @@
       <c r="A6" t="s">
         <v>123</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C6">
@@ -7984,7 +7979,7 @@
       <c r="A10" t="s">
         <v>124</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C10">
@@ -8106,7 +8101,7 @@
       <c r="A14" t="s">
         <v>125</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C14">
@@ -8228,7 +8223,7 @@
       <c r="A18" t="s">
         <v>126</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C18">
@@ -8263,7 +8258,7 @@
       <c r="A19" t="s">
         <v>127</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C19">
@@ -8385,7 +8380,7 @@
       <c r="A23" t="s">
         <v>129</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C23">
@@ -8507,7 +8502,7 @@
       <c r="A27" t="s">
         <v>130</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C27">
@@ -8542,7 +8537,7 @@
       <c r="A28" t="s">
         <v>131</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C28">
@@ -8664,7 +8659,7 @@
       <c r="A32" t="s">
         <v>132</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C32">
@@ -8699,7 +8694,7 @@
       <c r="A33" t="s">
         <v>133</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C33">
@@ -8821,7 +8816,7 @@
       <c r="A37" t="s">
         <v>134</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C37">
@@ -8856,7 +8851,7 @@
       <c r="A38" t="s">
         <v>135</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C38">
@@ -8891,7 +8886,7 @@
       <c r="A39" t="s">
         <v>136</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C39">
@@ -9013,7 +9008,7 @@
       <c r="A43" t="s">
         <v>137</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C43">
@@ -9048,7 +9043,7 @@
       <c r="A44" t="s">
         <v>138</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C44">
@@ -9083,8 +9078,8 @@
       <c r="A45" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>140</v>
+      <c r="B45" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C45">
         <v>64</v>
@@ -9116,10 +9111,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B46" t="s">
-        <v>142</v>
       </c>
       <c r="C46">
         <v>64</v>
@@ -9136,13 +9131,13 @@
       <c r="G46">
         <v>10</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I46" t="s">
         <v>14</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K46" t="s">
@@ -9151,10 +9146,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>143</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C47">
         <v>64</v>
@@ -9171,13 +9166,13 @@
       <c r="G47">
         <v>100</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I47" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="K47" t="s">
@@ -9185,13 +9180,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K46" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K47" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A39:L44 A1:L36 A37:C37 G37:J37 L37 A45 C45:L45 A46:G46 I46 K46:L46" numberStoredAsText="1"/>
+    <ignoredError sqref="K46:L46 I46 A46:G46 C44:L45 A44:A45 L37 G37:J37 A37:C37 A1:L36 A39:L43" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9239,7 +9234,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -9361,7 +9356,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -9483,7 +9478,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -9605,7 +9600,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -9727,7 +9722,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -9849,7 +9844,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
@@ -9884,10 +9879,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" t="s">
         <v>150</v>
-      </c>
-      <c r="B23" t="s">
-        <v>151</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -10006,10 +10001,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C27">
         <v>32</v>
@@ -10041,7 +10036,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -10163,7 +10158,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -10198,7 +10193,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -10320,7 +10315,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -10355,7 +10350,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -10477,7 +10472,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -10512,7 +10507,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -10547,7 +10542,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
@@ -10582,7 +10577,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -10670,7 +10665,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -10792,7 +10787,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -10914,7 +10909,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -11036,7 +11031,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -11158,7 +11153,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -11193,7 +11188,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -11315,10 +11310,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -11437,10 +11432,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C27">
         <v>32</v>
@@ -11472,7 +11467,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -11594,7 +11589,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
@@ -11629,7 +11624,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -11751,7 +11746,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -11786,7 +11781,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -11908,7 +11903,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -11943,7 +11938,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -11978,7 +11973,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
@@ -12013,7 +12008,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -12048,7 +12043,7 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B46" t="s">
         <v>51</v>
@@ -12088,7 +12083,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="I45:K45 A45:G45 A1:K44" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K44 A45:G45 I45:K45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12136,7 +12131,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -12166,15 +12161,15 @@
         <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -12201,15 +12196,15 @@
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -12236,15 +12231,15 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -12271,12 +12266,12 @@
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -12294,7 +12289,7 @@
         <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -12311,10 +12306,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -12329,7 +12324,7 @@
         <v>470</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -12346,10 +12341,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -12364,7 +12359,7 @@
         <v>970</v>
       </c>
       <c r="G8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -12381,10 +12376,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -12399,7 +12394,7 @@
         <v>1920</v>
       </c>
       <c r="G9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -12416,7 +12411,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -12434,7 +12429,7 @@
         <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -12451,10 +12446,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -12469,7 +12464,7 @@
         <v>455</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -12486,10 +12481,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -12504,7 +12499,7 @@
         <v>1105</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -12521,10 +12516,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C13">
         <v>32</v>
@@ -12539,7 +12534,7 @@
         <v>2255</v>
       </c>
       <c r="G13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -12556,7 +12551,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
@@ -12591,10 +12586,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -12626,10 +12621,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -12661,10 +12656,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17">
         <v>40</v>
@@ -12696,7 +12691,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -12714,7 +12709,7 @@
         <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -12726,15 +12721,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -12749,7 +12744,7 @@
         <v>305</v>
       </c>
       <c r="G19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -12761,15 +12756,15 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -12784,7 +12779,7 @@
         <v>855</v>
       </c>
       <c r="G20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -12796,15 +12791,15 @@
         <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C21">
         <v>32</v>
@@ -12819,7 +12814,7 @@
         <v>1905</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -12831,12 +12826,12 @@
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
@@ -12866,15 +12861,15 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -12901,15 +12896,15 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -12936,15 +12931,15 @@
         <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C25">
         <v>40</v>
@@ -12971,12 +12966,12 @@
         <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
@@ -12994,7 +12989,7 @@
         <v>238</v>
       </c>
       <c r="G26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -13011,10 +13006,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -13029,7 +13024,7 @@
         <v>555</v>
       </c>
       <c r="G27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -13046,10 +13041,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -13064,7 +13059,7 @@
         <v>1255</v>
       </c>
       <c r="G28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -13081,10 +13076,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C29">
         <v>32</v>
@@ -13099,7 +13094,7 @@
         <v>2505</v>
       </c>
       <c r="G29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -13116,7 +13111,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -13151,10 +13146,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -13186,10 +13181,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -13221,10 +13216,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C33">
         <v>40</v>
@@ -13256,7 +13251,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -13274,7 +13269,7 @@
         <v>125</v>
       </c>
       <c r="G34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -13291,10 +13286,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -13309,7 +13304,7 @@
         <v>370</v>
       </c>
       <c r="G35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -13326,10 +13321,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -13344,7 +13339,7 @@
         <v>820</v>
       </c>
       <c r="G36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -13361,10 +13356,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -13379,7 +13374,7 @@
         <v>1670</v>
       </c>
       <c r="G37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -13396,7 +13391,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
@@ -13414,7 +13409,7 @@
         <v>4700</v>
       </c>
       <c r="G38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -13431,7 +13426,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
@@ -13466,7 +13461,7 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -13484,7 +13479,7 @@
         <v>4250</v>
       </c>
       <c r="G40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -13496,12 +13491,12 @@
         <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
@@ -13531,12 +13526,12 @@
         <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -13554,7 +13549,7 @@
         <v>5100</v>
       </c>
       <c r="G42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -13571,7 +13566,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -13606,7 +13601,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B44" t="s">
         <v>32</v>
@@ -13641,7 +13636,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
@@ -13671,7 +13666,7 @@
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/法宝属性.xlsx
+++ b/法宝属性.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="7"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="金" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">水!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">火!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">土!$A$1:$K$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">雷!$A$1:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">雷!$A$1:$K$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">体!$A$1:$K$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="203">
   <si>
     <t>法宝名</t>
   </si>
@@ -549,6 +549,9 @@
     <t>惊雷兽吼</t>
   </si>
   <si>
+    <t>免罪阳雷</t>
+  </si>
+  <si>
     <t>雷元乌龙旗</t>
   </si>
   <si>
@@ -562,6 +565,9 @@
   </si>
   <si>
     <t>五雷号令</t>
+  </si>
+  <si>
+    <t>纠罚神雷</t>
   </si>
   <si>
     <t>大力丸</t>
@@ -1296,8 +1302,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
@@ -3333,7 +3340,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="K46 A46:G46 A1:K31 A32:G32 I32:K32 C45:K45 A45 A34:K44" numberStoredAsText="1"/>
+    <ignoredError sqref="A34:K44 A45 C45:K45 I32:K32 A32:G32 A1:K31 A46:G46 K46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4985,7 +4992,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A48:L49 A1:K47" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K47 A48:L49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8300,7 +8307,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.9166666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.9166666666667" style="3" customWidth="1"/>
     <col min="3" max="4" width="7.41666666666667" customWidth="1"/>
     <col min="5" max="5" width="5.41666666666667" customWidth="1"/>
     <col min="6" max="7" width="7.41666666666667" customWidth="1"/>
@@ -8313,7 +8320,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -8351,7 +8358,7 @@
       <c r="A2" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C2">
@@ -8485,7 +8492,7 @@
       <c r="A6" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6">
@@ -8619,7 +8626,7 @@
       <c r="A10" t="s">
         <v>126</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C10">
@@ -8753,7 +8760,7 @@
       <c r="A14" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C14">
@@ -8887,7 +8894,7 @@
       <c r="A18" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C18">
@@ -8925,7 +8932,7 @@
       <c r="A19" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C19">
@@ -9059,7 +9066,7 @@
       <c r="A23" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C23">
@@ -9193,7 +9200,7 @@
       <c r="A27" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C27">
@@ -9231,7 +9238,7 @@
       <c r="A28" t="s">
         <v>133</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C28">
@@ -9365,7 +9372,7 @@
       <c r="A32" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C32">
@@ -9403,7 +9410,7 @@
       <c r="A33" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C33">
@@ -9537,7 +9544,7 @@
       <c r="A37" t="s">
         <v>136</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C37">
@@ -9575,7 +9582,7 @@
       <c r="A38" t="s">
         <v>137</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C38">
@@ -9613,7 +9620,7 @@
       <c r="A39" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C39">
@@ -9747,7 +9754,7 @@
       <c r="A43" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C43">
@@ -9785,7 +9792,7 @@
       <c r="A44" t="s">
         <v>140</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C44">
@@ -9823,7 +9830,7 @@
       <c r="A45" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C45">
@@ -9861,7 +9868,7 @@
       <c r="A46" t="s">
         <v>142</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>143</v>
       </c>
       <c r="C46">
@@ -9899,7 +9906,7 @@
       <c r="A47" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C47">
@@ -9940,7 +9947,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="K46 I46 A46:G46 C44:K45 A44:A45 G37:J37 A37:C37 A1:K36 A39:K43" numberStoredAsText="1"/>
+    <ignoredError sqref="A39:K43 A1:K36 A37:C37 G37:J37 A44:A45 C44:K45 A46:G46 I46 K46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9948,7 +9955,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -11227,51 +11234,57 @@
         <v>158</v>
       </c>
       <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38">
+        <v>56</v>
+      </c>
+      <c r="D38">
+        <v>105</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
+      </c>
+      <c r="F38">
+        <v>4600</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
+        <v>27</v>
+      </c>
+      <c r="L38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" t="s">
         <v>48</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>5</v>
       </c>
-      <c r="D38">
-        <v>20</v>
-      </c>
-      <c r="E38">
+      <c r="D39">
+        <v>20</v>
+      </c>
+      <c r="E39">
         <v>3</v>
       </c>
-      <c r="F38">
+      <c r="F39">
         <v>500</v>
-      </c>
-      <c r="G38">
-        <v>50</v>
-      </c>
-      <c r="H38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" t="s">
-        <v>5</v>
-      </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="K38" t="s">
-        <v>130</v>
-      </c>
-      <c r="L38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="C39">
-        <v>12</v>
-      </c>
-      <c r="D39">
-        <v>32</v>
-      </c>
-      <c r="E39">
-        <v>5</v>
-      </c>
-      <c r="F39">
-        <v>1090</v>
       </c>
       <c r="G39">
         <v>50</v>
@@ -11283,7 +11296,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K39" t="s">
         <v>130</v>
@@ -11294,16 +11307,16 @@
     </row>
     <row r="40" spans="1:12">
       <c r="C40">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D40">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>2140</v>
+        <v>1090</v>
       </c>
       <c r="G40">
         <v>50</v>
@@ -11315,7 +11328,7 @@
         <v>5</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K40" t="s">
         <v>130</v>
@@ -11326,19 +11339,19 @@
     </row>
     <row r="41" spans="1:12">
       <c r="C41">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D41">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="E41">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F41">
-        <v>4140</v>
+        <v>2140</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H41" t="s">
         <v>31</v>
@@ -11347,7 +11360,7 @@
         <v>5</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s">
         <v>130</v>
@@ -11357,35 +11370,29 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" t="s">
-        <v>159</v>
-      </c>
-      <c r="B42" t="s">
-        <v>48</v>
-      </c>
       <c r="C42">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D42">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F42">
-        <v>5900</v>
+        <v>4140</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J42" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s">
         <v>130</v>
@@ -11399,34 +11406,34 @@
         <v>160</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C43">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D43">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F43">
-        <v>5350</v>
+        <v>5900</v>
       </c>
       <c r="G43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I43" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J43" t="s">
         <v>32</v>
       </c>
       <c r="K43" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="L43" t="s">
         <v>24</v>
@@ -11437,19 +11444,19 @@
         <v>161</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>64</v>
       </c>
       <c r="D44">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="E44">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F44">
-        <v>6250</v>
+        <v>5350</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -11464,7 +11471,7 @@
         <v>32</v>
       </c>
       <c r="K44" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="L44" t="s">
         <v>24</v>
@@ -11475,47 +11482,123 @@
         <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45">
         <v>64</v>
       </c>
       <c r="D45">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E45">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F45">
-        <v>6950</v>
+        <v>6250</v>
       </c>
       <c r="G45">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H45" t="s">
         <v>31</v>
       </c>
       <c r="I45" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
       </c>
       <c r="K45" t="s">
+        <v>64</v>
+      </c>
+      <c r="L45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46">
+        <v>64</v>
+      </c>
+      <c r="D46">
+        <v>108</v>
+      </c>
+      <c r="E46">
+        <v>18</v>
+      </c>
+      <c r="F46">
+        <v>6950</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" t="s">
         <v>130</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47">
+        <v>64</v>
+      </c>
+      <c r="D47">
+        <v>143</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>5100</v>
+      </c>
+      <c r="G47">
+        <v>50</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" t="s">
+        <v>27</v>
+      </c>
+      <c r="L47" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K45" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K46" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K200" numberStoredAsText="1"/>
+    <ignoredError sqref="A39:K45 A1:K37 A46:G46 I46:K46 A48:K201" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11575,7 +11658,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -11709,7 +11792,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -11843,7 +11926,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -11977,7 +12060,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s">
         <v>29</v>
@@ -12111,7 +12194,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
@@ -12149,7 +12232,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -12283,7 +12366,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s">
         <v>152</v>
@@ -12417,7 +12500,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s">
         <v>152</v>
@@ -12455,7 +12538,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s">
         <v>70</v>
@@ -12589,7 +12672,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s">
         <v>70</v>
@@ -12627,7 +12710,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s">
         <v>45</v>
@@ -12761,7 +12844,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
         <v>45</v>
@@ -12799,7 +12882,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
         <v>48</v>
@@ -12933,7 +13016,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s">
         <v>48</v>
@@ -12971,7 +13054,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -13009,7 +13092,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
@@ -13047,7 +13130,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -13085,7 +13168,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
@@ -13128,7 +13211,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A45:G45 I45:K45 A1:K44" numberStoredAsText="1"/>
+    <ignoredError sqref="A45:G45 A1:K44 I45:K45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13188,7 +13271,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -13218,7 +13301,7 @@
         <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -13226,10 +13309,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -13256,7 +13339,7 @@
         <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -13264,10 +13347,10 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -13294,7 +13377,7 @@
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -13302,10 +13385,10 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -13332,7 +13415,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -13340,7 +13423,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -13358,7 +13441,7 @@
         <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -13378,10 +13461,10 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -13396,7 +13479,7 @@
         <v>470</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -13416,10 +13499,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -13434,7 +13517,7 @@
         <v>970</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -13454,10 +13537,10 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -13472,7 +13555,7 @@
         <v>1920</v>
       </c>
       <c r="G9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -13492,7 +13575,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -13510,7 +13593,7 @@
         <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -13530,10 +13613,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -13548,7 +13631,7 @@
         <v>455</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -13568,10 +13651,10 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -13586,7 +13669,7 @@
         <v>1105</v>
       </c>
       <c r="G12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -13606,10 +13689,10 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C13">
         <v>32</v>
@@ -13624,7 +13707,7 @@
         <v>2255</v>
       </c>
       <c r="G13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -13644,7 +13727,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B14" t="s">
         <v>40</v>
@@ -13682,10 +13765,10 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -13720,10 +13803,10 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -13758,10 +13841,10 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C17">
         <v>40</v>
@@ -13796,7 +13879,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
@@ -13814,7 +13897,7 @@
         <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -13826,7 +13909,7 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s">
         <v>24</v>
@@ -13834,10 +13917,10 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -13852,7 +13935,7 @@
         <v>305</v>
       </c>
       <c r="G19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -13864,7 +13947,7 @@
         <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s">
         <v>24</v>
@@ -13872,10 +13955,10 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -13890,7 +13973,7 @@
         <v>855</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -13902,7 +13985,7 @@
         <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L20" t="s">
         <v>24</v>
@@ -13910,10 +13993,10 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C21">
         <v>32</v>
@@ -13928,7 +14011,7 @@
         <v>1905</v>
       </c>
       <c r="G21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -13940,7 +14023,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L21" t="s">
         <v>24</v>
@@ -13948,7 +14031,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
@@ -13978,7 +14061,7 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s">
         <v>24</v>
@@ -13986,10 +14069,10 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -14016,7 +14099,7 @@
         <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L23" t="s">
         <v>24</v>
@@ -14024,10 +14107,10 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -14054,7 +14137,7 @@
         <v>19</v>
       </c>
       <c r="K24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s">
         <v>24</v>
@@ -14062,10 +14145,10 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C25">
         <v>40</v>
@@ -14092,7 +14175,7 @@
         <v>20</v>
       </c>
       <c r="K25" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s">
         <v>24</v>
@@ -14100,7 +14183,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s">
         <v>38</v>
@@ -14118,7 +14201,7 @@
         <v>238</v>
       </c>
       <c r="G26" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -14138,10 +14221,10 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -14156,7 +14239,7 @@
         <v>555</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -14176,10 +14259,10 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -14194,7 +14277,7 @@
         <v>1255</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -14214,10 +14297,10 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C29">
         <v>32</v>
@@ -14232,7 +14315,7 @@
         <v>2505</v>
       </c>
       <c r="G29" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -14252,7 +14335,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B30" t="s">
         <v>45</v>
@@ -14290,10 +14373,10 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -14328,10 +14411,10 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -14366,10 +14449,10 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C33">
         <v>40</v>
@@ -14404,7 +14487,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -14422,7 +14505,7 @@
         <v>125</v>
       </c>
       <c r="G34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -14442,10 +14525,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -14460,7 +14543,7 @@
         <v>370</v>
       </c>
       <c r="G35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -14480,10 +14563,10 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -14498,7 +14581,7 @@
         <v>820</v>
       </c>
       <c r="G36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -14518,10 +14601,10 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -14536,7 +14619,7 @@
         <v>1670</v>
       </c>
       <c r="G37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -14556,7 +14639,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s">
         <v>40</v>
@@ -14574,7 +14657,7 @@
         <v>4700</v>
       </c>
       <c r="G38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -14594,7 +14677,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
         <v>55</v>
@@ -14632,7 +14715,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
         <v>48</v>
@@ -14650,7 +14733,7 @@
         <v>4250</v>
       </c>
       <c r="G40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -14662,7 +14745,7 @@
         <v>32</v>
       </c>
       <c r="K40" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s">
         <v>24</v>
@@ -14670,7 +14753,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
@@ -14700,7 +14783,7 @@
         <v>32</v>
       </c>
       <c r="K41" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s">
         <v>24</v>
@@ -14708,7 +14791,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
         <v>45</v>
@@ -14726,7 +14809,7 @@
         <v>5100</v>
       </c>
       <c r="G42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -14746,7 +14829,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -14784,7 +14867,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s">
         <v>34</v>
@@ -14822,7 +14905,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B45" t="s">
         <v>29</v>
@@ -14852,7 +14935,7 @@
         <v>32</v>
       </c>
       <c r="K45" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L45" t="s">
         <v>24</v>
